--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E607DE27-E2D4-40BB-82FA-732364F32D3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5614FE96-B3FB-4443-99AF-0F677CA358FB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C078B880-B52D-4BC2-B921-986E3BCB9561}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3058E6F-9112-460C-B85C-04EA8CE77281}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224BA994-59A7-4B5D-93FB-8A44BEA145D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C01ADB1D-0BBC-4B46-A775-081FAB749668}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5614FE96-B3FB-4443-99AF-0F677CA358FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8948283-9ECA-4D93-8BDC-CED743D6BFE5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3058E6F-9112-460C-B85C-04EA8CE77281}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA297759-9951-42D4-98AF-11CFAEBB77BD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C01ADB1D-0BBC-4B46-A775-081FAB749668}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160381C1-8035-4DD1-B6FD-7BC99517E788}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8948283-9ECA-4D93-8BDC-CED743D6BFE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC6B752-627D-4448-AA71-6C6D675F40FB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA297759-9951-42D4-98AF-11CFAEBB77BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D11164C8-F2A1-4000-B6FC-3EFC04536455}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160381C1-8035-4DD1-B6FD-7BC99517E788}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAAF1295-3B0C-4A2A-B472-27A371E8C554}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC6B752-627D-4448-AA71-6C6D675F40FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BC69A3-4FA1-4DD6-B40B-8A9F0E31713A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D11164C8-F2A1-4000-B6FC-3EFC04536455}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C8E061A-E4E0-4ACC-9C5D-989C2A0B572E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAAF1295-3B0C-4A2A-B472-27A371E8C554}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFDE7038-4155-41DA-ACD0-C85ABF6DE427}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3876,13 +3876,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{195F6F99-3491-4BF8-B4CB-3D4494B173F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{942A18DA-2518-4C99-B2EB-53661DE9B670}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BE52F85-5565-4B30-B3D2-A34718FF71D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA503D7-7D31-4F7D-A168-EFEE6EEF73D5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7D54044-F52B-40F2-94EC-04EBBCE79236}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDCDD02E-CAAB-425E-BD5F-A250E740284D}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3876,13 +3876,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{942A18DA-2518-4C99-B2EB-53661DE9B670}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FFDFC21-61E4-4A53-A0A5-59AFB4F1720F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA503D7-7D31-4F7D-A168-EFEE6EEF73D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3EF8194-2918-4FE4-9064-FF98B680A27A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDCDD02E-CAAB-425E-BD5F-A250E740284D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F352A3A5-4A19-4EE7-8962-971DEF102F34}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3598,291 +3598,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FFDFC21-61E4-4A53-A0A5-59AFB4F1720F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3EF8194-2918-4FE4-9064-FF98B680A27A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F352A3A5-4A19-4EE7-8962-971DEF102F34}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3598,4 +3598,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407628E9-53D2-4644-8AAE-D3369943B210}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8E9574-BE82-43E2-B257-83CADF7BAA7C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC2D2AF-D192-4A52-9F65-B56C3A8CED51}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3598,291 +3598,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407628E9-53D2-4644-8AAE-D3369943B210}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8E9574-BE82-43E2-B257-83CADF7BAA7C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC2D2AF-D192-4A52-9F65-B56C3A8CED51}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3598,4 +3598,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFF1836E-E7B1-4D15-9351-E8F64A549C75}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{187E7CA7-BCBD-459B-A44E-FB61B3C5801E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1AC703E-FD2A-49B0-A646-B3A500038405}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3876,13 +3876,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFF1836E-E7B1-4D15-9351-E8F64A549C75}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFCFC4E7-9900-4C95-9D18-1485F4F39D0E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{187E7CA7-BCBD-459B-A44E-FB61B3C5801E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4455BA5E-C2B4-4154-8EC6-26A08E7DACC4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1AC703E-FD2A-49B0-A646-B3A500038405}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC8FFD24-B4F0-4397-ACEB-C59C9CFEBDD7}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3876,13 +3876,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFCFC4E7-9900-4C95-9D18-1485F4F39D0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CB9B08C-BE93-482D-93BE-44432807436F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4455BA5E-C2B4-4154-8EC6-26A08E7DACC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89F47DD2-0F99-454A-80B9-1E4B9351F6F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC8FFD24-B4F0-4397-ACEB-C59C9CFEBDD7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4C74E8-1554-4C0D-BF99-0331EDD546EA}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3876,13 +3876,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CB9B08C-BE93-482D-93BE-44432807436F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A268D69E-F6B6-424F-B795-E9F83013E433}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89F47DD2-0F99-454A-80B9-1E4B9351F6F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81EEEC32-1640-4B20-9B22-98B4480B06DD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D4C74E8-1554-4C0D-BF99-0331EDD546EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2B0926-1900-4DAA-95C0-ADAB9129C378}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3876,13 +3876,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A268D69E-F6B6-424F-B795-E9F83013E433}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBB5844-74CE-4FB9-93F4-D2021B16FCE9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81EEEC32-1640-4B20-9B22-98B4480B06DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD4C6DE9-020C-4D82-9466-FEECFA5CE8CB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2B0926-1900-4DAA-95C0-ADAB9129C378}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04C9428F-9FED-4EB1-A156-90456DD5C6A8}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3876,13 +3876,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBB5844-74CE-4FB9-93F4-D2021B16FCE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8775CCBC-EF82-4DEA-94CC-DFD6103F355F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD4C6DE9-020C-4D82-9466-FEECFA5CE8CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37FD81CB-B2B5-4493-A805-3404EAC89B76}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04C9428F-9FED-4EB1-A156-90456DD5C6A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3380272-6AC6-4518-BB43-8CD8D752C70B}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3598,291 +3598,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8775CCBC-EF82-4DEA-94CC-DFD6103F355F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37FD81CB-B2B5-4493-A805-3404EAC89B76}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3380272-6AC6-4518-BB43-8CD8D752C70B}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3598,4 +3598,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035C160D-543E-4A17-BC59-3A2EC97BB856}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366FD8C-6D5B-46BB-A0BF-EBBDDA2713F0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8B42A58-6405-4BA7-99B2-47617880783A}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="121">
   <si>
     <t>species_sci</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Varecia variegata rubra</t>
   </si>
   <si>
-    <t>Varecia variegata</t>
-  </si>
-  <si>
     <t>Varecia variegata variegata</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
     <t>Callimico goeldii</t>
   </si>
   <si>
-    <t>Callithrix pygmaea</t>
-  </si>
-  <si>
     <t>Cebuella pygmaea</t>
   </si>
   <si>
@@ -265,9 +259,6 @@
     <t>Ateles paniscus</t>
   </si>
   <si>
-    <t>Lagothrix lagothricha</t>
-  </si>
-  <si>
     <t>Lagothrix lagotricha</t>
   </si>
   <si>
@@ -380,9 +371,6 @@
   </si>
   <si>
     <t>Pan troglodytes</t>
-  </si>
-  <si>
-    <t>Pongo sp.</t>
   </si>
   <si>
     <t>Pongo abelii</t>
@@ -1467,7 +1455,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47">
         <v>1.40007561095226</v>
@@ -1484,7 +1472,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48">
         <v>1.02204135552313</v>
@@ -1498,10 +1486,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49">
         <v>1.15243525834186</v>
@@ -1515,10 +1503,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C50">
         <v>1.14885486473691</v>
@@ -1529,10 +1517,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <v>0.422365483073509</v>
@@ -1546,10 +1534,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C52">
         <v>0.548153076997243</v>
@@ -1563,10 +1551,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C53">
         <v>1.37244158736962</v>
@@ -1580,10 +1568,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C54">
         <v>1.00425154506567</v>
@@ -1597,10 +1585,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55">
         <v>0.971287708335438</v>
@@ -1614,10 +1602,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C56">
         <v>0.873376471896216</v>
@@ -1631,10 +1619,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C57">
         <v>0.861711959324643</v>
@@ -1648,10 +1636,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C58">
         <v>1.00743328732766</v>
@@ -1665,10 +1653,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C59">
         <v>0.471393486810094</v>
@@ -1682,10 +1670,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60">
         <v>1.10856520816426</v>
@@ -1699,10 +1687,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C61">
         <v>0.904363612551585</v>
@@ -1716,10 +1704,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62">
         <v>1.05168775175858</v>
@@ -1733,10 +1721,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63">
         <v>1.05876776435606</v>
@@ -1750,10 +1738,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C64">
         <v>0.984301599047729</v>
@@ -1767,10 +1755,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C65">
         <v>1.56568356541191</v>
@@ -1784,10 +1772,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C66">
         <v>1.23783848230913</v>
@@ -1801,10 +1789,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C67">
         <v>1.32325697190067</v>
@@ -1818,10 +1806,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C68">
         <v>1.22865832658758</v>
@@ -1835,10 +1823,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C69">
         <v>1.64214160038655</v>
@@ -1852,10 +1840,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C70">
         <v>1.11825939911062</v>
@@ -1869,10 +1857,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B71" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C71">
         <v>1.68794192463035</v>
@@ -1886,10 +1874,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C72">
         <v>1.1706981366311</v>
@@ -1903,10 +1891,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C73">
         <v>1.63379907179792</v>
@@ -1920,10 +1908,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C74">
         <v>1.38602395226123</v>
@@ -1937,10 +1925,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C75">
         <v>1.11906615148242</v>
@@ -1954,10 +1942,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C76">
         <v>1.45292642084593</v>
@@ -1971,10 +1959,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C77">
         <v>0.603777419267949</v>
@@ -1988,10 +1976,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C78">
         <v>0.9954182990798069</v>
@@ -2005,10 +1993,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B79" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C79">
         <v>1.29137383119401</v>
@@ -2022,10 +2010,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C80">
         <v>1.86810866495463</v>
@@ -2039,10 +2027,10 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B81" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C81">
         <v>0.565419018216477</v>
@@ -2053,10 +2041,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C82">
         <v>0.746032664714785</v>
@@ -2070,10 +2058,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C83">
         <v>0.687435750503355</v>
@@ -2087,10 +2075,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C84">
         <v>1.83687468245124</v>
@@ -2104,10 +2092,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C85">
         <v>1.72195921899077</v>
@@ -2121,10 +2109,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C86">
         <v>0.572553670038598</v>
@@ -2138,10 +2126,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C87">
         <v>1.17177927393802</v>
@@ -2155,10 +2143,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C88">
         <v>1.02033299817418</v>
@@ -2172,10 +2160,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C89">
         <v>0.996761565305023</v>
@@ -2189,10 +2177,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B90" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C90">
         <v>0.856631621709061</v>
@@ -2206,10 +2194,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C91">
         <v>1.7365976046442</v>
@@ -2223,10 +2211,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C92">
         <v>1.85590101661237</v>
@@ -2240,10 +2228,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B93" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C93">
         <v>1.03218172597006</v>
@@ -2254,10 +2242,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C94">
         <v>0.798357325771174</v>
@@ -2271,10 +2259,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C95">
         <v>1.63124668194915</v>
@@ -2288,10 +2276,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B96" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C96">
         <v>1.52127517730103</v>
@@ -2305,10 +2293,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C97">
         <v>1.60859743143501</v>
@@ -2322,10 +2310,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C98">
         <v>1.18941283574095</v>
@@ -2339,10 +2327,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C99">
         <v>1.02435269982441</v>
@@ -2356,10 +2344,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C100">
         <v>0.769977746756403</v>
@@ -2373,10 +2361,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C101">
         <v>0.866746465060363</v>
@@ -2390,10 +2378,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B102" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C102">
         <v>0.230466836328381</v>
@@ -2404,10 +2392,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C103">
         <v>0.600482908245825</v>
@@ -2421,10 +2409,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B104" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C104">
         <v>1.2507418086443</v>
@@ -2438,10 +2426,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C105">
         <v>1.80198696987699</v>
@@ -2452,10 +2440,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B106" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C106">
         <v>1.29373888903011</v>
@@ -2469,10 +2457,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B107" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C107">
         <v>1.59346219516623</v>
@@ -2486,10 +2474,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B108" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C108">
         <v>1.08219553003877</v>
@@ -2503,10 +2491,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B109" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C109">
         <v>1.33620994116696</v>
@@ -2520,10 +2508,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B110" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C110">
         <v>1.76983447403569</v>
@@ -2537,10 +2525,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B111" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C111">
         <v>1.24664005984697</v>
@@ -2554,10 +2542,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B112" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C112">
         <v>1.49855655449966</v>
@@ -2571,10 +2559,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B113" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C113">
         <v>1.67997850986382</v>
@@ -2588,10 +2576,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B114" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C114">
         <v>1.47520015673735</v>
@@ -2605,10 +2593,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C115">
         <v>0.880131209732712</v>
@@ -2622,10 +2610,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C116">
         <v>1.30149934390842</v>
@@ -2639,10 +2627,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C117">
         <v>0.863629884719384</v>
@@ -2653,10 +2641,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C118">
         <v>1.30031419276679</v>
@@ -2667,10 +2655,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B119" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C119">
         <v>1.33315983861591</v>
@@ -2681,10 +2669,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B120" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C120">
         <v>1.11068369147808</v>
@@ -2698,10 +2686,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B121" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C121">
         <v>1.11414224879738</v>
@@ -2715,10 +2703,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B122" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C122">
         <v>1.01907599999383</v>
@@ -2732,10 +2720,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B123" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C123">
         <v>1.07339249913053</v>
@@ -2746,10 +2734,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B124" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C124">
         <v>0.509101870244824</v>
@@ -2763,10 +2751,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B125" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C125">
         <v>1.15397234190199</v>
@@ -2780,10 +2768,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B126" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C126">
         <v>0.164594459315598</v>
@@ -2797,10 +2785,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B127" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C127">
         <v>0.643896378966053</v>
@@ -2811,10 +2799,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B128" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C128">
         <v>1.23184052217936</v>
@@ -2828,10 +2816,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B129" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C129">
         <v>1.03618623761807</v>
@@ -2845,10 +2833,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B130" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C130">
         <v>0.80440397625966</v>
@@ -2859,10 +2847,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B131" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C131">
         <v>1.02674163828187</v>
@@ -2876,10 +2864,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B132" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C132">
         <v>1.36153853780977</v>
@@ -2890,10 +2878,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B133" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C133">
         <v>1.24280524484049</v>
@@ -2904,10 +2892,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B134" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C134">
         <v>1.28738289862955</v>
@@ -2918,10 +2906,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B135" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C135">
         <v>1.27618355697741</v>
@@ -2935,10 +2923,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B136" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C136">
         <v>1.35034733690939</v>
@@ -2952,10 +2940,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B137" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C137">
         <v>1.17402880124957</v>
@@ -2969,10 +2957,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B138" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C138">
         <v>1.29758530370833</v>
@@ -2986,10 +2974,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B139" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C139">
         <v>1.66796169081866</v>
@@ -3003,10 +2991,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B140" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C140">
         <v>1.28263841381107</v>
@@ -3020,10 +3008,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B141" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C141">
         <v>1.41868231852566</v>
@@ -3034,10 +3022,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B142" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C142">
         <v>1.45030358547205</v>
@@ -3048,10 +3036,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B143" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C143">
         <v>1.27276673020437</v>
@@ -3065,10 +3053,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B144" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C144">
         <v>1.35929449357798</v>
@@ -3082,10 +3070,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B145" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C145">
         <v>0.914285581467099</v>
@@ -3099,10 +3087,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B146" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C146">
         <v>1.01677920543083</v>
@@ -3113,10 +3101,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B147" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C147">
         <v>1.09113888121898</v>
@@ -3130,10 +3118,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B148" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C148">
         <v>0.880966134812287</v>
@@ -3147,10 +3135,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B149" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C149">
         <v>1.27772088326507</v>
@@ -3161,10 +3149,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B150" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C150">
         <v>1.339198489722</v>
@@ -3175,10 +3163,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B151" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C151">
         <v>1.11352363236587</v>
@@ -3192,10 +3180,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B152" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C152">
         <v>0.930549435609321</v>
@@ -3209,10 +3197,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B153" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C153">
         <v>1.46623688969866</v>
@@ -3226,10 +3214,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B154" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C154">
         <v>0.906064001662483</v>
@@ -3243,10 +3231,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B155" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C155">
         <v>1.08697816813994</v>
@@ -3260,10 +3248,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B156" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C156">
         <v>1.13906067375477</v>
@@ -3277,10 +3265,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B157" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C157">
         <v>0.566784872290849</v>
@@ -3294,10 +3282,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B158" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C158">
         <v>1.12300989482099</v>
@@ -3308,10 +3296,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B159" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C159">
         <v>0.6390318596501769</v>
@@ -3325,10 +3313,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B160" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C160">
         <v>0.9583789783973931</v>
@@ -3342,10 +3330,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B161" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C161">
         <v>0.188053654103712</v>
@@ -3359,10 +3347,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B162" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C162">
         <v>1.64480703854916</v>
@@ -3376,10 +3364,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B163" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C163">
         <v>1.47027618755211</v>
@@ -3393,10 +3381,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B164" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C164">
         <v>0.375029668019445</v>
@@ -3410,10 +3398,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B165" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C165">
         <v>0.0880625034256728</v>
@@ -3427,10 +3415,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B166" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C166">
         <v>0.08824635905080359</v>
@@ -3444,10 +3432,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B167" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C167">
         <v>0.308668325547446</v>
@@ -3461,10 +3449,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B168" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C168">
         <v>0.283014430815863</v>
@@ -3478,10 +3466,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B169" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C169">
         <v>0.503824234295893</v>
@@ -3495,10 +3483,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B170" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C170">
         <v>0.962557200938976</v>
@@ -3512,10 +3500,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B171" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C171">
         <v>2.03067787197455</v>
@@ -3529,10 +3517,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B172" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C172">
         <v>1.38150120846112</v>
@@ -3546,10 +3534,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B173" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C173">
         <v>1.47334647078267</v>
@@ -3563,10 +3551,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B174" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C174">
         <v>1.44966380886263</v>
@@ -3580,10 +3568,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B175" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C175">
         <v>1.64527536380398</v>
@@ -3876,13 +3864,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{035C160D-543E-4A17-BC59-3A2EC97BB856}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A5EFBC-A813-4788-AD1C-E4F590D40AD1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6366FD8C-6D5B-46BB-A0BF-EBBDDA2713F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7FBDC01-C0B4-424F-8607-BA3CC4B422B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8B42A58-6405-4BA7-99B2-47617880783A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33F6C7D8-42CF-400B-84CC-CF513FE57A50}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3864,13 +3864,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A5EFBC-A813-4788-AD1C-E4F590D40AD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74EE703A-AE5B-4917-8685-1326FBD0B2A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7FBDC01-C0B4-424F-8607-BA3CC4B422B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9311061F-C29F-484D-9B8A-C4F099685FF8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33F6C7D8-42CF-400B-84CC-CF513FE57A50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FBFB916-7BE9-48FE-A86B-F2955DFA299F}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3864,13 +3864,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74EE703A-AE5B-4917-8685-1326FBD0B2A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{547746E1-F922-4000-B2D5-30B43D68C696}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9311061F-C29F-484D-9B8A-C4F099685FF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39C1E5C7-6E0A-49A1-8113-3D4241CF9E13}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FBFB916-7BE9-48FE-A86B-F2955DFA299F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E92F969-096A-4872-A551-9FEC00F8D04A}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3864,13 +3864,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{547746E1-F922-4000-B2D5-30B43D68C696}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2B869D3-7EFD-49B3-9AAC-021E081B6FA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39C1E5C7-6E0A-49A1-8113-3D4241CF9E13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DAE867B-A6C7-4743-920A-AC26FB33F8C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E92F969-096A-4872-A551-9FEC00F8D04A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{518FC21A-9233-4A8B-98A7-3B2272CAB20B}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3864,13 +3864,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2B869D3-7EFD-49B3-9AAC-021E081B6FA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{089A3BA9-3285-49EE-BEA2-5C264B049BB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DAE867B-A6C7-4743-920A-AC26FB33F8C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A473E45-3DA5-4737-9D8A-70E3CEB5F64E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{518FC21A-9233-4A8B-98A7-3B2272CAB20B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EE67F8-8DCA-495F-9285-A51BB067FFD7}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3586,291 +3586,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{089A3BA9-3285-49EE-BEA2-5C264B049BB9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A473E45-3DA5-4737-9D8A-70E3CEB5F64E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EE67F8-8DCA-495F-9285-A51BB067FFD7}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -3586,4 +3586,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5C4A016-FF52-4A5A-8DD0-6CEFFB2EF3B0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15DF59CF-B087-43AA-AFE8-07A624A809BF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67D0917A-57DD-477E-B2C8-ECE43E0EC741}"/>
 </file>